--- a/static/modelos/descricao_lote_imp.xlsx
+++ b/static/modelos/descricao_lote_imp.xlsx
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="245">
   <si>
     <t xml:space="preserve">Titulo</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t xml:space="preserve">CargoSuperiorImediato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adicional</t>
   </si>
   <si>
     <t xml:space="preserve">Incluir a Area</t>
@@ -916,8 +919,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.33"/>
@@ -948,6 +951,9 @@
       </c>
       <c r="G1" s="0" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -997,14 +1003,14 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.89"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1024,14 +1030,14 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="13.33"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1051,7 +1057,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28.33"/>
@@ -1062,7 +1068,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1070,7 +1076,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1078,7 +1084,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1086,7 +1092,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1094,7 +1100,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1102,7 +1108,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1110,7 +1116,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1118,7 +1124,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1126,7 +1132,7 @@
         <v>24</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1134,7 +1140,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1142,7 +1148,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1150,7 +1156,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1158,7 +1164,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1166,7 +1172,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1174,7 +1180,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1182,7 +1188,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1190,7 +1196,7 @@
         <v>26</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1198,7 +1204,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1206,7 +1212,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1214,7 +1220,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1222,7 +1228,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1230,7 +1236,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1238,7 +1244,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1246,7 +1252,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1254,7 +1260,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1262,7 +1268,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1282,7 +1288,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AG203"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46.1"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="0" width="28.33"/>
@@ -1314,10 +1320,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
@@ -1358,16 +1364,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
@@ -1401,91 +1407,91 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L3" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M3" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N3" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O3" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P3" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R3" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S3" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T3" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U3" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V3" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W3" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="X3" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y3" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Z3" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA3" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AB3" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AC3" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD3" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AE3" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AF3" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AG3" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1493,91 +1499,91 @@
         <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="0" t="s">
-        <v>9</v>
-      </c>
       <c r="H4" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J4" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L4" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M4" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N4" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O4" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P4" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="R4" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="S4" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="T4" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="U4" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="V4" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="W4" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="X4" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Y4" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Z4" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AA4" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AB4" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AC4" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AD4" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AE4" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AF4" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AG4" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1585,76 +1591,76 @@
         <v>4</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L5" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M5" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O5" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P5" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R5" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S5" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="U5" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="V5" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X5" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Z5" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AA5" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB5" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC5" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AD5" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE5" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AF5" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AG5" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1662,70 +1668,70 @@
         <v>5</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J6" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L6" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M6" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P6" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="R6" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="S6" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="U6" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V6" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="X6" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Z6" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA6" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AB6" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AC6" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AD6" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AE6" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG6" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1733,61 +1739,61 @@
         <v>6</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K7" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M7" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="R7" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="S7" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U7" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="X7" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Z7" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AA7" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AB7" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC7" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AD7" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AE7" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG7" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1795,55 +1801,55 @@
         <v>7</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K8" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M8" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="R8" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="S8" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="U8" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="X8" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Z8" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AB8" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AC8" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AD8" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AE8" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG8" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1851,52 +1857,52 @@
         <v>8</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C9" s="0" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K9" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M9" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="R9" s="0" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="S9" s="0" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="U9" s="0" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="X9" s="0" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Z9" s="0" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AB9" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AC9" s="0" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AE9" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG9" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1904,49 +1910,49 @@
         <v>9</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C10" s="0" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M10" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R10" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S10" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U10" s="0" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="X10" s="0" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Z10" s="0" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AB10" s="0" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AC10" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AE10" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG10" s="0" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1954,46 +1960,46 @@
         <v>10</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C11" s="0" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M11" s="0" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R11" s="0" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="S11" s="0" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U11" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="X11" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Z11" s="0" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AC11" s="0" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AE11" s="0" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG11" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2001,46 +2007,46 @@
         <v>11</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" s="0" t="n">
         <v>2</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M12" s="0" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="R12" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="S12" s="0" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="U12" s="0" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="X12" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Z12" s="0" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AC12" s="0" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AE12" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AG12" s="0" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2048,40 +2054,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C13" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M13" s="0" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="S13" s="0" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="U13" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="X13" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z13" s="0" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC13" s="0" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG13" s="0" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2089,34 +2095,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C14" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M14" s="0" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="U14" s="0" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="X14" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Z14" s="0" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AC14" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG14" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2124,31 +2130,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C15" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M15" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="U15" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Z15" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AC15" s="0" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG15" s="0" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2156,28 +2162,28 @@
         <v>16</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M16" s="0" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="U16" s="0" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AC16" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG16" s="0" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2185,25 +2191,25 @@
         <v>17</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C17" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E17" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="U17" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="0" t="s">
-        <v>194</v>
-      </c>
-      <c r="U17" s="0" t="s">
-        <v>22</v>
-      </c>
       <c r="AC17" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG17" s="0" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2211,25 +2217,25 @@
         <v>18</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C18" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="U18" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AC18" s="0" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG18" s="0" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2237,25 +2243,25 @@
         <v>19</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C19" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="U19" s="0" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AC19" s="0" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG19" s="0" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2263,25 +2269,25 @@
         <v>20</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C20" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="U20" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AC20" s="0" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG20" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2289,25 +2295,25 @@
         <v>22</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C21" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="U21" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AC21" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG21" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2315,19 +2321,19 @@
         <v>23</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C22" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="U22" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG22" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2335,19 +2341,19 @@
         <v>24</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C23" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="U23" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG23" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2355,19 +2361,19 @@
         <v>25</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C24" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="U24" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG24" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2375,19 +2381,19 @@
         <v>26</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C25" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="U25" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AG25" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2395,19 +2401,19 @@
         <v>27</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C26" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U26" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG26" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2415,16 +2421,16 @@
         <v>28</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C27" s="0" t="n">
         <v>4</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U27" s="0" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2432,16 +2438,16 @@
         <v>29</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C28" s="0" t="n">
         <v>4</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U28" s="0" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2449,7 +2455,7 @@
         <v>30</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C29" s="0" t="n">
         <v>4</v>
@@ -2460,7 +2466,7 @@
         <v>31</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C30" s="0" t="n">
         <v>4</v>
@@ -2471,7 +2477,7 @@
         <v>32</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C31" s="0" t="n">
         <v>5</v>
@@ -2482,7 +2488,7 @@
         <v>33</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C32" s="0" t="n">
         <v>5</v>
@@ -2493,7 +2499,7 @@
         <v>34</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C33" s="0" t="n">
         <v>5</v>
@@ -2504,7 +2510,7 @@
         <v>35</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C34" s="0" t="n">
         <v>5</v>
@@ -2515,7 +2521,7 @@
         <v>36</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C35" s="0" t="n">
         <v>5</v>
@@ -2526,7 +2532,7 @@
         <v>37</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C36" s="0" t="n">
         <v>5</v>
@@ -2537,7 +2543,7 @@
         <v>38</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C37" s="0" t="n">
         <v>6</v>
@@ -2548,7 +2554,7 @@
         <v>40</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C38" s="0" t="n">
         <v>6</v>
@@ -2559,7 +2565,7 @@
         <v>41</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C39" s="0" t="n">
         <v>6</v>
@@ -2570,7 +2576,7 @@
         <v>42</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C40" s="0" t="n">
         <v>7</v>
@@ -2581,7 +2587,7 @@
         <v>43</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C41" s="0" t="n">
         <v>7</v>
@@ -2592,7 +2598,7 @@
         <v>44</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C42" s="0" t="n">
         <v>7</v>
@@ -2603,7 +2609,7 @@
         <v>45</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C43" s="0" t="n">
         <v>7</v>
@@ -2614,7 +2620,7 @@
         <v>46</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C44" s="0" t="n">
         <v>7</v>
@@ -2625,7 +2631,7 @@
         <v>47</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C45" s="0" t="n">
         <v>7</v>
@@ -2636,7 +2642,7 @@
         <v>48</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C46" s="0" t="n">
         <v>7</v>
@@ -2647,7 +2653,7 @@
         <v>49</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C47" s="0" t="n">
         <v>7</v>
@@ -2658,7 +2664,7 @@
         <v>50</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C48" s="0" t="n">
         <v>7</v>
@@ -2669,7 +2675,7 @@
         <v>51</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C49" s="0" t="n">
         <v>7</v>
@@ -2680,7 +2686,7 @@
         <v>52</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C50" s="0" t="n">
         <v>7</v>
@@ -2691,7 +2697,7 @@
         <v>53</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C51" s="0" t="n">
         <v>7</v>
@@ -2702,7 +2708,7 @@
         <v>54</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C52" s="0" t="n">
         <v>7</v>
@@ -2713,7 +2719,7 @@
         <v>55</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>8</v>
@@ -2724,7 +2730,7 @@
         <v>56</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>9</v>
@@ -2735,7 +2741,7 @@
         <v>57</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>9</v>
@@ -2746,7 +2752,7 @@
         <v>58</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C56" s="0" t="n">
         <v>9</v>
@@ -2757,7 +2763,7 @@
         <v>59</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C57" s="0" t="n">
         <v>10</v>
@@ -2768,7 +2774,7 @@
         <v>60</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C58" s="0" t="n">
         <v>10</v>
@@ -2779,7 +2785,7 @@
         <v>61</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C59" s="0" t="n">
         <v>10</v>
@@ -2790,7 +2796,7 @@
         <v>62</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C60" s="0" t="n">
         <v>10</v>
@@ -2801,7 +2807,7 @@
         <v>63</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C61" s="0" t="n">
         <v>10</v>
@@ -2812,7 +2818,7 @@
         <v>64</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C62" s="0" t="n">
         <v>10</v>
@@ -2823,7 +2829,7 @@
         <v>65</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C63" s="0" t="n">
         <v>10</v>
@@ -2834,7 +2840,7 @@
         <v>66</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C64" s="0" t="n">
         <v>10</v>
@@ -2845,7 +2851,7 @@
         <v>67</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C65" s="0" t="n">
         <v>10</v>
@@ -2856,7 +2862,7 @@
         <v>68</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C66" s="0" t="n">
         <v>11</v>
@@ -2867,7 +2873,7 @@
         <v>69</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C67" s="0" t="n">
         <v>11</v>
@@ -2878,7 +2884,7 @@
         <v>70</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C68" s="0" t="n">
         <v>11</v>
@@ -2889,7 +2895,7 @@
         <v>71</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C69" s="0" t="n">
         <v>11</v>
@@ -2900,7 +2906,7 @@
         <v>72</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C70" s="0" t="n">
         <v>11</v>
@@ -2911,7 +2917,7 @@
         <v>73</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C71" s="0" t="n">
         <v>11</v>
@@ -2922,7 +2928,7 @@
         <v>74</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C72" s="0" t="n">
         <v>11</v>
@@ -2933,7 +2939,7 @@
         <v>75</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C73" s="0" t="n">
         <v>11</v>
@@ -2944,7 +2950,7 @@
         <v>76</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C74" s="0" t="n">
         <v>11</v>
@@ -2955,7 +2961,7 @@
         <v>77</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C75" s="0" t="n">
         <v>11</v>
@@ -2966,7 +2972,7 @@
         <v>78</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C76" s="0" t="n">
         <v>12</v>
@@ -2977,7 +2983,7 @@
         <v>79</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C77" s="0" t="n">
         <v>13</v>
@@ -2988,7 +2994,7 @@
         <v>80</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C78" s="0" t="n">
         <v>13</v>
@@ -2999,7 +3005,7 @@
         <v>81</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C79" s="0" t="n">
         <v>13</v>
@@ -3010,7 +3016,7 @@
         <v>82</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C80" s="0" t="n">
         <v>13</v>
@@ -3021,7 +3027,7 @@
         <v>83</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C81" s="0" t="n">
         <v>13</v>
@@ -3032,7 +3038,7 @@
         <v>84</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C82" s="0" t="n">
         <v>13</v>
@@ -3043,7 +3049,7 @@
         <v>85</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C83" s="0" t="n">
         <v>13</v>
@@ -3054,7 +3060,7 @@
         <v>86</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C84" s="0" t="n">
         <v>13</v>
@@ -3065,7 +3071,7 @@
         <v>87</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C85" s="0" t="n">
         <v>13</v>
@@ -3076,7 +3082,7 @@
         <v>88</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C86" s="0" t="n">
         <v>13</v>
@@ -3087,7 +3093,7 @@
         <v>89</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C87" s="0" t="n">
         <v>13</v>
@@ -3098,7 +3104,7 @@
         <v>90</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C88" s="0" t="n">
         <v>13</v>
@@ -3109,7 +3115,7 @@
         <v>91</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C89" s="0" t="n">
         <v>13</v>
@@ -3120,7 +3126,7 @@
         <v>92</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C90" s="0" t="n">
         <v>13</v>
@@ -3131,7 +3137,7 @@
         <v>93</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C91" s="0" t="n">
         <v>13</v>
@@ -3142,7 +3148,7 @@
         <v>94</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C92" s="0" t="n">
         <v>13</v>
@@ -3153,7 +3159,7 @@
         <v>95</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C93" s="0" t="n">
         <v>13</v>
@@ -3164,7 +3170,7 @@
         <v>96</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C94" s="0" t="n">
         <v>13</v>
@@ -3175,7 +3181,7 @@
         <v>97</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C95" s="0" t="n">
         <v>13</v>
@@ -3186,7 +3192,7 @@
         <v>98</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C96" s="0" t="n">
         <v>13</v>
@@ -3197,7 +3203,7 @@
         <v>99</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C97" s="0" t="n">
         <v>3</v>
@@ -3208,7 +3214,7 @@
         <v>100</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C98" s="0" t="n">
         <v>14</v>
@@ -3219,7 +3225,7 @@
         <v>101</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C99" s="0" t="n">
         <v>14</v>
@@ -3230,7 +3236,7 @@
         <v>102</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C100" s="0" t="n">
         <v>14</v>
@@ -3241,7 +3247,7 @@
         <v>103</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C101" s="0" t="n">
         <v>15</v>
@@ -3252,7 +3258,7 @@
         <v>104</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C102" s="0" t="n">
         <v>16</v>
@@ -3263,7 +3269,7 @@
         <v>105</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C103" s="0" t="n">
         <v>16</v>
@@ -3274,7 +3280,7 @@
         <v>106</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C104" s="0" t="n">
         <v>16</v>
@@ -3285,7 +3291,7 @@
         <v>107</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C105" s="0" t="n">
         <v>16</v>
@@ -3296,7 +3302,7 @@
         <v>108</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C106" s="0" t="n">
         <v>16</v>
@@ -3307,7 +3313,7 @@
         <v>109</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C107" s="0" t="n">
         <v>16</v>
@@ -3318,7 +3324,7 @@
         <v>110</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C108" s="0" t="n">
         <v>16</v>
@@ -3329,7 +3335,7 @@
         <v>111</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C109" s="0" t="n">
         <v>16</v>
@@ -3340,7 +3346,7 @@
         <v>112</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C110" s="0" t="n">
         <v>16</v>
@@ -3351,7 +3357,7 @@
         <v>113</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C111" s="0" t="n">
         <v>16</v>
@@ -3362,7 +3368,7 @@
         <v>114</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C112" s="0" t="n">
         <v>16</v>
@@ -3373,7 +3379,7 @@
         <v>115</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C113" s="0" t="n">
         <v>17</v>
@@ -3384,7 +3390,7 @@
         <v>116</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C114" s="0" t="n">
         <v>17</v>
@@ -3395,7 +3401,7 @@
         <v>117</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C115" s="0" t="n">
         <v>17</v>
@@ -3406,7 +3412,7 @@
         <v>118</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C116" s="0" t="n">
         <v>17</v>
@@ -3417,7 +3423,7 @@
         <v>119</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C117" s="0" t="n">
         <v>18</v>
@@ -3428,7 +3434,7 @@
         <v>120</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C118" s="0" t="n">
         <v>18</v>
@@ -3439,7 +3445,7 @@
         <v>121</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C119" s="0" t="n">
         <v>18</v>
@@ -3450,7 +3456,7 @@
         <v>122</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C120" s="0" t="n">
         <v>18</v>
@@ -3461,7 +3467,7 @@
         <v>123</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C121" s="0" t="n">
         <v>18</v>
@@ -3472,7 +3478,7 @@
         <v>124</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C122" s="0" t="n">
         <v>18</v>
@@ -3483,7 +3489,7 @@
         <v>125</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C123" s="0" t="n">
         <v>18</v>
@@ -3494,7 +3500,7 @@
         <v>126</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C124" s="0" t="n">
         <v>19</v>
@@ -3505,7 +3511,7 @@
         <v>127</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C125" s="0" t="n">
         <v>19</v>
@@ -3516,7 +3522,7 @@
         <v>128</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C126" s="0" t="n">
         <v>19</v>
@@ -3527,7 +3533,7 @@
         <v>129</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C127" s="0" t="n">
         <v>19</v>
@@ -3538,7 +3544,7 @@
         <v>130</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C128" s="0" t="n">
         <v>19</v>
@@ -3549,7 +3555,7 @@
         <v>131</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C129" s="0" t="n">
         <v>19</v>
@@ -3560,7 +3566,7 @@
         <v>132</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C130" s="0" t="n">
         <v>19</v>
@@ -3571,7 +3577,7 @@
         <v>133</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C131" s="0" t="n">
         <v>19</v>
@@ -3582,7 +3588,7 @@
         <v>134</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C132" s="0" t="n">
         <v>19</v>
@@ -3593,7 +3599,7 @@
         <v>135</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C133" s="0" t="n">
         <v>19</v>
@@ -3604,7 +3610,7 @@
         <v>136</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C134" s="0" t="n">
         <v>19</v>
@@ -3615,7 +3621,7 @@
         <v>137</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C135" s="0" t="n">
         <v>19</v>
@@ -3626,7 +3632,7 @@
         <v>138</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C136" s="0" t="n">
         <v>19</v>
@@ -3637,7 +3643,7 @@
         <v>139</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C137" s="0" t="n">
         <v>19</v>
@@ -3648,7 +3654,7 @@
         <v>140</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C138" s="0" t="n">
         <v>19</v>
@@ -3659,7 +3665,7 @@
         <v>141</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C139" s="0" t="n">
         <v>19</v>
@@ -3670,7 +3676,7 @@
         <v>142</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C140" s="0" t="n">
         <v>19</v>
@@ -3681,7 +3687,7 @@
         <v>143</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C141" s="0" t="n">
         <v>20</v>
@@ -3692,7 +3698,7 @@
         <v>144</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C142" s="0" t="n">
         <v>25</v>
@@ -3703,7 +3709,7 @@
         <v>145</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C143" s="0" t="n">
         <v>20</v>
@@ -3714,7 +3720,7 @@
         <v>146</v>
       </c>
       <c r="B144" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C144" s="0" t="n">
         <v>20</v>
@@ -3725,7 +3731,7 @@
         <v>147</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C145" s="0" t="n">
         <v>20</v>
@@ -3736,7 +3742,7 @@
         <v>148</v>
       </c>
       <c r="B146" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C146" s="0" t="n">
         <v>21</v>
@@ -3747,7 +3753,7 @@
         <v>149</v>
       </c>
       <c r="B147" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C147" s="0" t="n">
         <v>21</v>
@@ -3758,7 +3764,7 @@
         <v>150</v>
       </c>
       <c r="B148" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C148" s="0" t="n">
         <v>21</v>
@@ -3769,7 +3775,7 @@
         <v>151</v>
       </c>
       <c r="B149" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C149" s="0" t="n">
         <v>21</v>
@@ -3780,7 +3786,7 @@
         <v>152</v>
       </c>
       <c r="B150" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C150" s="0" t="n">
         <v>21</v>
@@ -3791,7 +3797,7 @@
         <v>153</v>
       </c>
       <c r="B151" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C151" s="0" t="n">
         <v>21</v>
@@ -3802,7 +3808,7 @@
         <v>154</v>
       </c>
       <c r="B152" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C152" s="0" t="n">
         <v>21</v>
@@ -3813,7 +3819,7 @@
         <v>155</v>
       </c>
       <c r="B153" s="0" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C153" s="0" t="n">
         <v>21</v>
@@ -3824,7 +3830,7 @@
         <v>156</v>
       </c>
       <c r="B154" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C154" s="0" t="n">
         <v>21</v>
@@ -3835,7 +3841,7 @@
         <v>157</v>
       </c>
       <c r="B155" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C155" s="0" t="n">
         <v>22</v>
@@ -3846,7 +3852,7 @@
         <v>158</v>
       </c>
       <c r="B156" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C156" s="0" t="n">
         <v>23</v>
@@ -3857,7 +3863,7 @@
         <v>159</v>
       </c>
       <c r="B157" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C157" s="0" t="n">
         <v>23</v>
@@ -3868,7 +3874,7 @@
         <v>160</v>
       </c>
       <c r="B158" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C158" s="0" t="n">
         <v>23</v>
@@ -3879,7 +3885,7 @@
         <v>161</v>
       </c>
       <c r="B159" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C159" s="0" t="n">
         <v>23</v>
@@ -3890,7 +3896,7 @@
         <v>162</v>
       </c>
       <c r="B160" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C160" s="0" t="n">
         <v>23</v>
@@ -3901,7 +3907,7 @@
         <v>163</v>
       </c>
       <c r="B161" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C161" s="0" t="n">
         <v>23</v>
@@ -3912,7 +3918,7 @@
         <v>164</v>
       </c>
       <c r="B162" s="0" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C162" s="0" t="n">
         <v>23</v>
@@ -3923,7 +3929,7 @@
         <v>165</v>
       </c>
       <c r="B163" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C163" s="0" t="n">
         <v>23</v>
@@ -3934,7 +3940,7 @@
         <v>166</v>
       </c>
       <c r="B164" s="0" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C164" s="0" t="n">
         <v>23</v>
@@ -3945,7 +3951,7 @@
         <v>167</v>
       </c>
       <c r="B165" s="0" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C165" s="0" t="n">
         <v>23</v>
@@ -3956,7 +3962,7 @@
         <v>168</v>
       </c>
       <c r="B166" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C166" s="0" t="n">
         <v>23</v>
@@ -3967,7 +3973,7 @@
         <v>169</v>
       </c>
       <c r="B167" s="0" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C167" s="0" t="n">
         <v>23</v>
@@ -3978,7 +3984,7 @@
         <v>170</v>
       </c>
       <c r="B168" s="0" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C168" s="0" t="n">
         <v>23</v>
@@ -3989,7 +3995,7 @@
         <v>171</v>
       </c>
       <c r="B169" s="0" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C169" s="0" t="n">
         <v>23</v>
@@ -4000,7 +4006,7 @@
         <v>172</v>
       </c>
       <c r="B170" s="0" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C170" s="0" t="n">
         <v>23</v>
@@ -4011,7 +4017,7 @@
         <v>173</v>
       </c>
       <c r="B171" s="0" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C171" s="0" t="n">
         <v>23</v>
@@ -4022,7 +4028,7 @@
         <v>174</v>
       </c>
       <c r="B172" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C172" s="0" t="n">
         <v>23</v>
@@ -4033,7 +4039,7 @@
         <v>175</v>
       </c>
       <c r="B173" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C173" s="0" t="n">
         <v>23</v>
@@ -4044,7 +4050,7 @@
         <v>176</v>
       </c>
       <c r="B174" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C174" s="0" t="n">
         <v>23</v>
@@ -4055,7 +4061,7 @@
         <v>177</v>
       </c>
       <c r="B175" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C175" s="0" t="n">
         <v>23</v>
@@ -4066,7 +4072,7 @@
         <v>178</v>
       </c>
       <c r="B176" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C176" s="0" t="n">
         <v>23</v>
@@ -4077,7 +4083,7 @@
         <v>179</v>
       </c>
       <c r="B177" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C177" s="0" t="n">
         <v>23</v>
@@ -4088,7 +4094,7 @@
         <v>180</v>
       </c>
       <c r="B178" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C178" s="0" t="n">
         <v>22</v>
@@ -4099,7 +4105,7 @@
         <v>181</v>
       </c>
       <c r="B179" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C179" s="0" t="n">
         <v>24</v>
@@ -4110,7 +4116,7 @@
         <v>182</v>
       </c>
       <c r="B180" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C180" s="0" t="n">
         <v>19</v>
@@ -4121,7 +4127,7 @@
         <v>183</v>
       </c>
       <c r="B181" s="0" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C181" s="0" t="n">
         <v>3</v>
@@ -4132,7 +4138,7 @@
         <v>184</v>
       </c>
       <c r="B182" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C182" s="0" t="n">
         <v>23</v>
@@ -4143,7 +4149,7 @@
         <v>185</v>
       </c>
       <c r="B183" s="0" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C183" s="0" t="n">
         <v>3</v>
@@ -4154,7 +4160,7 @@
         <v>186</v>
       </c>
       <c r="B184" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C184" s="0" t="n">
         <v>3</v>
@@ -4165,7 +4171,7 @@
         <v>187</v>
       </c>
       <c r="B185" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C185" s="0" t="n">
         <v>26</v>
@@ -4176,7 +4182,7 @@
         <v>188</v>
       </c>
       <c r="B186" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C186" s="0" t="n">
         <v>26</v>
@@ -4187,7 +4193,7 @@
         <v>189</v>
       </c>
       <c r="B187" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C187" s="0" t="n">
         <v>26</v>
@@ -4198,7 +4204,7 @@
         <v>190</v>
       </c>
       <c r="B188" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C188" s="0" t="n">
         <v>26</v>
@@ -4209,7 +4215,7 @@
         <v>191</v>
       </c>
       <c r="B189" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C189" s="0" t="n">
         <v>26</v>
@@ -4220,7 +4226,7 @@
         <v>192</v>
       </c>
       <c r="B190" s="0" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C190" s="0" t="n">
         <v>26</v>
@@ -4231,7 +4237,7 @@
         <v>193</v>
       </c>
       <c r="B191" s="0" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C191" s="0" t="n">
         <v>26</v>
@@ -4242,7 +4248,7 @@
         <v>194</v>
       </c>
       <c r="B192" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C192" s="0" t="n">
         <v>26</v>
@@ -4253,7 +4259,7 @@
         <v>195</v>
       </c>
       <c r="B193" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C193" s="0" t="n">
         <v>26</v>
@@ -4264,7 +4270,7 @@
         <v>196</v>
       </c>
       <c r="B194" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C194" s="0" t="n">
         <v>26</v>
@@ -4275,7 +4281,7 @@
         <v>197</v>
       </c>
       <c r="B195" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C195" s="0" t="n">
         <v>26</v>
@@ -4286,7 +4292,7 @@
         <v>198</v>
       </c>
       <c r="B196" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C196" s="0" t="n">
         <v>20</v>
@@ -4297,7 +4303,7 @@
         <v>199</v>
       </c>
       <c r="B197" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C197" s="0" t="n">
         <v>24</v>
@@ -4308,7 +4314,7 @@
         <v>200</v>
       </c>
       <c r="B198" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C198" s="0" t="n">
         <v>13</v>
@@ -4319,7 +4325,7 @@
         <v>201</v>
       </c>
       <c r="B199" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C199" s="0" t="n">
         <v>16</v>
@@ -4330,7 +4336,7 @@
         <v>202</v>
       </c>
       <c r="B200" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C200" s="0" t="n">
         <v>13</v>
@@ -4341,7 +4347,7 @@
         <v>203</v>
       </c>
       <c r="B201" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C201" s="0" t="n">
         <v>13</v>
@@ -4352,7 +4358,7 @@
         <v>204</v>
       </c>
       <c r="B202" s="0" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C202" s="0" t="n">
         <v>13</v>
@@ -4363,7 +4369,7 @@
         <v>205</v>
       </c>
       <c r="B203" s="0" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C203" s="0" t="n">
         <v>13</v>
@@ -4391,119 +4397,119 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32.11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>

--- a/static/modelos/descricao_lote_imp.xlsx
+++ b/static/modelos/descricao_lote_imp.xlsx
@@ -14,35 +14,38 @@
     <sheet name="Familia" sheetId="4" state="visible" r:id="rId5"/>
     <sheet name="Sub Familia" sheetId="5" state="visible" r:id="rId6"/>
     <sheet name="Nivel" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="Planilha7" sheetId="7" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'Sub Familia'!$A$1:$AG$203</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'Sub Familia'!$A$1:$AI$203</definedName>
     <definedName function="false" hidden="false" name="Administrativo" vbProcedure="false">'Sub Familia'!$G$3:$G$13</definedName>
     <definedName function="false" hidden="false" name="Auditoria" vbProcedure="false">'Sub Familia'!$H$4</definedName>
     <definedName function="false" hidden="false" name="Comercial" vbProcedure="false">'Sub Familia'!$I$4:$I$22</definedName>
     <definedName function="false" hidden="false" name="Comunicação" vbProcedure="false">'Sub Familia'!$J$4:$J$7</definedName>
     <definedName function="false" hidden="false" name="Controladoria" vbProcedure="false">'Sub Familia'!$K$4:$K$9</definedName>
-    <definedName function="false" hidden="false" name="Engenharia" vbProcedure="false">'Sub Familia'!$L$4:$L$6</definedName>
-    <definedName function="false" hidden="false" name="Financeiro" vbProcedure="false">'Sub Familia'!$M$4:$M$16</definedName>
-    <definedName function="false" hidden="false" name="Gerenciamento_de_Riscos" vbProcedure="false">'Sub Familia'!$N$4</definedName>
-    <definedName function="false" hidden="false" name="Gestão" vbProcedure="false">'Sub Familia'!$O$4:$O$5</definedName>
-    <definedName function="false" hidden="false" name="Importação_e_Exportação" vbProcedure="false">'Sub Familia'!$P$4:$P$6</definedName>
-    <definedName function="false" hidden="false" name="Jurídico" vbProcedure="false">'Sub Familia'!$R$4:$R$12</definedName>
-    <definedName function="false" hidden="false" name="Logística" vbProcedure="false">'Sub Familia'!$S$4:$S$13</definedName>
-    <definedName function="false" hidden="false" name="Manutenção" vbProcedure="false">'Sub Familia'!$U$4:$U$28</definedName>
-    <definedName function="false" hidden="false" name="Marketing" vbProcedure="false">'Sub Familia'!$V$4:$V$6</definedName>
-    <definedName function="false" hidden="false" name="MA_Mergers_and_Acquisitions" vbProcedure="false">'Sub Familia'!$T$4</definedName>
-    <definedName function="false" hidden="false" name="Meio_Ambiente" vbProcedure="false">'Sub Familia'!$W$4</definedName>
-    <definedName function="false" hidden="false" name="Mineração" vbProcedure="false">'Sub Familia'!$X$4:$X$14</definedName>
-    <definedName function="false" hidden="false" name="Novos_Negócios" vbProcedure="false">'Sub Familia'!$Y$4</definedName>
-    <definedName function="false" hidden="false" name="Operação" vbProcedure="false">'Sub Familia'!$Z$4:$Z$15</definedName>
-    <definedName function="false" hidden="false" name="Projetos" vbProcedure="false">'Sub Familia'!$AA$4:$AA$7</definedName>
-    <definedName function="false" hidden="false" name="Qualidade" vbProcedure="false">'Sub Familia'!$AB$4:$AB$10</definedName>
-    <definedName function="false" hidden="false" name="Recursos_Humanos" vbProcedure="false">'Sub Familia'!$AC$4:$AC$21</definedName>
-    <definedName function="false" hidden="false" name="Saúde_e_Segurança_do_Trabalho" vbProcedure="false">'Sub Familia'!$AD$4:$AD$8</definedName>
-    <definedName function="false" hidden="false" name="Suprimentos" vbProcedure="false">'Sub Familia'!$AE$4:$AE$12</definedName>
-    <definedName function="false" hidden="false" name="Sustentabilidade" vbProcedure="false">'Sub Familia'!$AF$4:$AF$5</definedName>
-    <definedName function="false" hidden="false" name="Tecnologia_da_Informação" vbProcedure="false">'Sub Familia'!$AG$4:$AG$29</definedName>
+    <definedName function="false" hidden="false" name="Editorial" vbProcedure="false">'Sub Familia'!$L$4:$L$17</definedName>
+    <definedName function="false" hidden="false" name="Educação" vbProcedure="false">'Sub Familia'!$M$4:$M$7</definedName>
+    <definedName function="false" hidden="false" name="Engenharia" vbProcedure="false">'Sub Familia'!$N$4:$N$6</definedName>
+    <definedName function="false" hidden="false" name="Financeiro" vbProcedure="false">'Sub Familia'!$O$4:$O$16</definedName>
+    <definedName function="false" hidden="false" name="Gerenciamento_de_Riscos" vbProcedure="false">'Sub Familia'!$P$4</definedName>
+    <definedName function="false" hidden="false" name="Gestão" vbProcedure="false">'Sub Familia'!$Q$4:$Q$5</definedName>
+    <definedName function="false" hidden="false" name="Importação_e_Exportação" vbProcedure="false">'Sub Familia'!$R$4:$R$6</definedName>
+    <definedName function="false" hidden="false" name="Jurídico" vbProcedure="false">'Sub Familia'!$T$4:$T$12</definedName>
+    <definedName function="false" hidden="false" name="Logística" vbProcedure="false">'Sub Familia'!$U$4:$U$13</definedName>
+    <definedName function="false" hidden="false" name="Manutenção" vbProcedure="false">'Sub Familia'!$W$4:$W$28</definedName>
+    <definedName function="false" hidden="false" name="Marketing" vbProcedure="false">'Sub Familia'!$X$4:$X$6</definedName>
+    <definedName function="false" hidden="false" name="MA_Mergers_and_Acquisitions" vbProcedure="false">'Sub Familia'!$V$4</definedName>
+    <definedName function="false" hidden="false" name="Meio_Ambiente" vbProcedure="false">'Sub Familia'!$Y$4</definedName>
+    <definedName function="false" hidden="false" name="Mineração" vbProcedure="false">'Sub Familia'!$Z$4:$Z$14</definedName>
+    <definedName function="false" hidden="false" name="Novos_Negócios" vbProcedure="false">'Sub Familia'!$AA$4</definedName>
+    <definedName function="false" hidden="false" name="Operação" vbProcedure="false">'Sub Familia'!$AB$4:$AB$15</definedName>
+    <definedName function="false" hidden="false" name="Projetos" vbProcedure="false">'Sub Familia'!$AC$4:$AC$7</definedName>
+    <definedName function="false" hidden="false" name="Qualidade" vbProcedure="false">'Sub Familia'!$AD$4:$AD$10</definedName>
+    <definedName function="false" hidden="false" name="Recursos_Humanos" vbProcedure="false">'Sub Familia'!$AE$4:$AE$21</definedName>
+    <definedName function="false" hidden="false" name="Saúde_e_Segurança_do_Trabalho" vbProcedure="false">'Sub Familia'!$AF$4:$AF$8</definedName>
+    <definedName function="false" hidden="false" name="Suprimentos" vbProcedure="false">'Sub Familia'!$AG$4:$AG$12</definedName>
+    <definedName function="false" hidden="false" name="Sustentabilidade" vbProcedure="false">'Sub Familia'!$AH$4:$AH$5</definedName>
+    <definedName function="false" hidden="false" name="Tecnologia_da_Informação" vbProcedure="false">'Sub Familia'!$AI$4:$AI$29</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -54,9 +57,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="245">
-  <si>
-    <t xml:space="preserve">Titulo</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="264">
+  <si>
+    <t xml:space="preserve">Titulodocargo</t>
   </si>
   <si>
     <t xml:space="preserve">Area</t>
@@ -104,6 +107,12 @@
     <t xml:space="preserve">Engenharia</t>
   </si>
   <si>
+    <t xml:space="preserve">Editorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Educação</t>
+  </si>
+  <si>
     <t xml:space="preserve">Financeiro</t>
   </si>
   <si>
@@ -209,6 +218,12 @@
     <t xml:space="preserve">Contabilidade</t>
   </si>
   <si>
+    <t xml:space="preserve">Arte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formação Ensino Médio</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automação</t>
   </si>
   <si>
@@ -266,6 +281,12 @@
     <t xml:space="preserve">Comunicação Externa</t>
   </si>
   <si>
+    <t xml:space="preserve">Arte Digital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formação Fundamental</t>
+  </si>
+  <si>
     <t xml:space="preserve">Contas a Pagar</t>
   </si>
   <si>
@@ -320,6 +341,12 @@
     <t xml:space="preserve">Custos</t>
   </si>
   <si>
+    <t xml:space="preserve">Conteúdo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedagógico</t>
+  </si>
+  <si>
     <t xml:space="preserve">Engenharia de Processos</t>
   </si>
   <si>
@@ -371,6 +398,12 @@
     <t xml:space="preserve">Fiscal</t>
   </si>
   <si>
+    <t xml:space="preserve">Conteúdo Digital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Psicopedagógico</t>
+  </si>
+  <si>
     <t xml:space="preserve">Crédito</t>
   </si>
   <si>
@@ -410,6 +443,9 @@
     <t xml:space="preserve">Fiscal Tributário</t>
   </si>
   <si>
+    <t xml:space="preserve">Designer Editorial</t>
+  </si>
+  <si>
     <t xml:space="preserve">Crédito e Cobrança</t>
   </si>
   <si>
@@ -485,6 +521,9 @@
     <t xml:space="preserve">Gestão de Contratos</t>
   </si>
   <si>
+    <t xml:space="preserve">Editorial Digital</t>
+  </si>
+  <si>
     <t xml:space="preserve">Eletrônico</t>
   </si>
   <si>
@@ -512,6 +551,9 @@
     <t xml:space="preserve">Licitação</t>
   </si>
   <si>
+    <t xml:space="preserve">Ilustração</t>
+  </si>
+  <si>
     <t xml:space="preserve">Planejamento Estratégico</t>
   </si>
   <si>
@@ -542,6 +584,9 @@
     <t xml:space="preserve">Merchandising</t>
   </si>
   <si>
+    <t xml:space="preserve">Produção Editorial</t>
+  </si>
+  <si>
     <t xml:space="preserve">Planejamento Financeiro</t>
   </si>
   <si>
@@ -566,6 +611,9 @@
     <t xml:space="preserve">Engenharia de Dados</t>
   </si>
   <si>
+    <t xml:space="preserve">Viagens/Logística de pessoas</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pré Vendas</t>
   </si>
   <si>
@@ -590,6 +638,9 @@
     <t xml:space="preserve">Precificação</t>
   </si>
   <si>
+    <t xml:space="preserve">Produção Gráfica</t>
+  </si>
+  <si>
     <t xml:space="preserve">Relação com Investidores</t>
   </si>
   <si>
@@ -629,6 +680,9 @@
     <t xml:space="preserve">Trade Marketing</t>
   </si>
   <si>
+    <t xml:space="preserve">Revisão de Texto</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tesouraria</t>
   </si>
   <si>
@@ -644,6 +698,9 @@
     <t xml:space="preserve">Vendas</t>
   </si>
   <si>
+    <t xml:space="preserve">Roteiro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Responsabilidade Social</t>
   </si>
   <si>
@@ -723,6 +780,9 @@
   </si>
   <si>
     <t xml:space="preserve">Programação de Manutenção</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Designer Digital</t>
   </si>
   <si>
     <t xml:space="preserve">Assistente</t>
@@ -920,7 +980,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.33"/>
@@ -957,33 +1017,29 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="7">
+  <dataValidations count="6">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E2:E1001" type="list">
       <formula1>INDIRECT(D2)</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Selecione uma opção da Lista!!" errorStyle="stop" errorTitle="Dado Invalido" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C3:C25" type="list">
-      <formula1>Subarea!$A$1:$A$26</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="false" error="Selecione uma opção da Lista!!" errorStyle="stop" errorTitle="Dado Invalido" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F2:F25" type="list">
+    <dataValidation allowBlank="false" error="Selecione uma opção da Lista!!" errorStyle="stop" errorTitle="Dado Invalido" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F2:F500" type="list">
       <formula1>Nivel!$A$1:$A$499</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Selecione uma opção da Lista!!" errorStyle="stop" errorTitle="Dado Invalido" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B3:B25" type="list">
-      <formula1>Area!$A$1:$A$500</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D2:D38" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D3:D500" type="list">
       <formula1>Familia!$B$1:$B$26</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Selecione uma opção da Lista!!" errorStyle="stop" errorTitle="Dado Invalido" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2" type="list">
+    <dataValidation allowBlank="false" error="Selecione uma opção da Lista!!" errorStyle="stop" errorTitle="Dado Invalido" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B500" type="list">
       <formula1>Area!$A$2:$A$500</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Selecione uma opção da Lista!!" errorStyle="stop" errorTitle="Dado Invalido" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C2" type="list">
+    <dataValidation allowBlank="false" error="Selecione uma opção da Lista!!" errorStyle="stop" errorTitle="Dado Invalido" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C2:C500" type="list">
       <formula1>Subarea!$A$2:$A$500</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D2" type="list">
+      <formula1>Familia!$B$1:$B$500</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -1003,7 +1059,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.89"/>
   </cols>
@@ -1030,7 +1086,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="13.33"/>
   </cols>
@@ -1056,8 +1112,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28.33"/>
@@ -1113,7 +1169,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>16</v>
@@ -1121,7 +1177,7 @@
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="n">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>17</v>
@@ -1129,7 +1185,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>18</v>
@@ -1137,7 +1193,7 @@
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>19</v>
@@ -1145,7 +1201,7 @@
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>20</v>
@@ -1153,7 +1209,7 @@
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>21</v>
@@ -1161,7 +1217,7 @@
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B13" s="0" t="s">
         <v>22</v>
@@ -1169,7 +1225,7 @@
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>23</v>
@@ -1177,7 +1233,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>24</v>
@@ -1185,7 +1241,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>25</v>
@@ -1193,7 +1249,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B17" s="0" t="s">
         <v>26</v>
@@ -1201,7 +1257,7 @@
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B18" s="0" t="s">
         <v>27</v>
@@ -1209,7 +1265,7 @@
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B19" s="0" t="s">
         <v>28</v>
@@ -1217,7 +1273,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B20" s="0" t="s">
         <v>29</v>
@@ -1225,7 +1281,7 @@
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B21" s="0" t="s">
         <v>30</v>
@@ -1233,7 +1289,7 @@
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B22" s="0" t="s">
         <v>31</v>
@@ -1241,7 +1297,7 @@
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B23" s="0" t="s">
         <v>32</v>
@@ -1249,7 +1305,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B24" s="0" t="s">
         <v>33</v>
@@ -1257,7 +1313,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B25" s="0" t="s">
         <v>34</v>
@@ -1265,13 +1321,35 @@
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>35</v>
       </c>
     </row>
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B33" type="list">
+      <formula1>Familia!$B$1:$B$500</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1287,43 +1365,43 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AG203"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AI222"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46.1"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="0" width="28.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="27.92"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="25.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="19.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="17.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="22.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="22.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="20.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="22.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="20.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="27.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="28.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="13.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="45.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="14.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="31.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="20.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="29.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="28.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="24.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="0" width="14.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="22.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="12" style="0" width="22.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="0" width="22.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="20.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="22.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="20.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="27.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="28.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="13.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="45.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="14.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="31.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="20.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="29.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="0" width="28.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="24.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="0" width="14.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="22.66"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
@@ -1358,6 +1436,8 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
       <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
@@ -1370,10 +1450,10 @@
         <v>1</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
@@ -1401,13 +1481,15 @@
       <c r="AE2" s="2"/>
       <c r="AF2" s="2"/>
       <c r="AG2" s="2"/>
+      <c r="AH2" s="2"/>
+      <c r="AI2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>1</v>
@@ -1431,25 +1513,25 @@
         <v>14</v>
       </c>
       <c r="L3" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="N3" s="0" t="s">
         <v>15</v>
-      </c>
-      <c r="M3" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="N3" s="0" t="s">
-        <v>41</v>
       </c>
       <c r="O3" s="0" t="s">
         <v>18</v>
       </c>
       <c r="P3" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="Q3" s="0" t="s">
+        <v>20</v>
       </c>
       <c r="R3" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="S3" s="0" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="T3" s="0" t="s">
         <v>22</v>
@@ -1461,37 +1543,43 @@
         <v>24</v>
       </c>
       <c r="W3" s="0" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="X3" s="0" t="s">
         <v>26</v>
       </c>
       <c r="Y3" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Z3" s="0" t="s">
         <v>28</v>
       </c>
       <c r="AA3" s="0" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="AB3" s="0" t="s">
         <v>30</v>
       </c>
       <c r="AC3" s="0" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="AD3" s="0" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AE3" s="0" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="AF3" s="0" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG3" s="0" t="s">
-        <v>47</v>
+        <v>35</v>
+      </c>
+      <c r="AH3" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI3" s="0" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1499,7 +1587,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>1</v>
@@ -1508,82 +1596,88 @@
         <v>11</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="H4" s="0" t="s">
         <v>11</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J4" s="0" t="s">
         <v>13</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L4" s="0" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M4" s="0" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N4" s="0" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="O4" s="0" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="P4" s="0" t="s">
-        <v>53</v>
+        <v>43</v>
+      </c>
+      <c r="Q4" s="0" t="s">
+        <v>20</v>
       </c>
       <c r="R4" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="S4" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T4" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="U4" s="0" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="V4" s="0" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="W4" s="0" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="X4" s="0" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="Y4" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Z4" s="0" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="AA4" s="0" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="AB4" s="0" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AC4" s="0" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AD4" s="0" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AE4" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AF4" s="0" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="AG4" s="0" t="s">
-        <v>66</v>
+        <v>69</v>
+      </c>
+      <c r="AH4" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI4" s="0" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1591,7 +1685,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>1</v>
@@ -1600,67 +1694,73 @@
         <v>12</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K5" s="0" t="s">
         <v>14</v>
       </c>
       <c r="L5" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="M5" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="M5" s="0" t="s">
-        <v>70</v>
-      </c>
       <c r="O5" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="P5" s="0" t="s">
-        <v>42</v>
+        <v>76</v>
+      </c>
+      <c r="Q5" s="0" t="s">
+        <v>77</v>
       </c>
       <c r="R5" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="S5" s="0" t="s">
-        <v>73</v>
+        <v>44</v>
+      </c>
+      <c r="T5" s="0" t="s">
+        <v>78</v>
       </c>
       <c r="U5" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="V5" s="0" t="s">
-        <v>24</v>
+        <v>79</v>
+      </c>
+      <c r="W5" s="0" t="s">
+        <v>80</v>
       </c>
       <c r="X5" s="0" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="Z5" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA5" s="0" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AB5" s="0" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AC5" s="0" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AD5" s="0" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="AE5" s="0" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="AF5" s="0" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="AG5" s="0" t="s">
-        <v>83</v>
+        <v>87</v>
+      </c>
+      <c r="AH5" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI5" s="0" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1668,7 +1768,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>1</v>
@@ -1677,61 +1777,67 @@
         <v>13</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="J6" s="0" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="L6" s="0" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="M6" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="P6" s="0" t="s">
-        <v>90</v>
+        <v>95</v>
+      </c>
+      <c r="N6" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="O6" s="0" t="s">
+        <v>97</v>
       </c>
       <c r="R6" s="0" t="s">
-        <v>91</v>
-      </c>
-      <c r="S6" s="0" t="s">
-        <v>92</v>
+        <v>98</v>
+      </c>
+      <c r="T6" s="0" t="s">
+        <v>99</v>
       </c>
       <c r="U6" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="V6" s="0" t="s">
-        <v>94</v>
+        <v>100</v>
+      </c>
+      <c r="W6" s="0" t="s">
+        <v>101</v>
       </c>
       <c r="X6" s="0" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="Z6" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA6" s="0" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="AB6" s="0" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="AC6" s="0" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="AD6" s="0" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="AE6" s="0" t="s">
-        <v>100</v>
+        <v>106</v>
+      </c>
+      <c r="AF6" s="0" t="s">
+        <v>107</v>
       </c>
       <c r="AG6" s="0" t="s">
-        <v>101</v>
+        <v>108</v>
+      </c>
+      <c r="AI6" s="0" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1739,7 +1845,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>1</v>
@@ -1748,52 +1854,58 @@
         <v>14</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="I7" s="0" t="s">
         <v>12</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="K7" s="0" t="s">
-        <v>104</v>
+        <v>112</v>
+      </c>
+      <c r="L7" s="0" t="s">
+        <v>113</v>
       </c>
       <c r="M7" s="0" t="s">
-        <v>105</v>
-      </c>
-      <c r="R7" s="0" t="s">
-        <v>106</v>
-      </c>
-      <c r="S7" s="0" t="s">
-        <v>107</v>
+        <v>114</v>
+      </c>
+      <c r="O7" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="T7" s="0" t="s">
+        <v>116</v>
       </c>
       <c r="U7" s="0" t="s">
-        <v>108</v>
-      </c>
-      <c r="X7" s="0" t="s">
-        <v>109</v>
+        <v>117</v>
+      </c>
+      <c r="W7" s="0" t="s">
+        <v>118</v>
       </c>
       <c r="Z7" s="0" t="s">
-        <v>110</v>
-      </c>
-      <c r="AA7" s="0" t="s">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c r="AB7" s="0" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="AC7" s="0" t="s">
-        <v>112</v>
+        <v>31</v>
       </c>
       <c r="AD7" s="0" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="AE7" s="0" t="s">
-        <v>113</v>
+        <v>122</v>
+      </c>
+      <c r="AF7" s="0" t="s">
+        <v>48</v>
       </c>
       <c r="AG7" s="0" t="s">
-        <v>114</v>
+        <v>123</v>
+      </c>
+      <c r="AI7" s="0" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1801,7 +1913,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>1</v>
@@ -1810,46 +1922,49 @@
         <v>15</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="K8" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="M8" s="0" t="s">
-        <v>118</v>
-      </c>
-      <c r="R8" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="S8" s="0" t="s">
-        <v>120</v>
+        <v>127</v>
+      </c>
+      <c r="L8" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="O8" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="T8" s="0" t="s">
+        <v>130</v>
       </c>
       <c r="U8" s="0" t="s">
-        <v>121</v>
-      </c>
-      <c r="X8" s="0" t="s">
-        <v>122</v>
+        <v>131</v>
+      </c>
+      <c r="W8" s="0" t="s">
+        <v>132</v>
       </c>
       <c r="Z8" s="0" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="AB8" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="AC8" s="0" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="AD8" s="0" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="AE8" s="0" t="s">
-        <v>127</v>
+        <v>136</v>
+      </c>
+      <c r="AF8" s="0" t="s">
+        <v>137</v>
       </c>
       <c r="AG8" s="0" t="s">
-        <v>128</v>
+        <v>138</v>
+      </c>
+      <c r="AI8" s="0" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1857,52 +1972,55 @@
         <v>8</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C9" s="0" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="I9" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="K9" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="L9" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="0" t="s">
-        <v>102</v>
-      </c>
-      <c r="I9" s="0" t="s">
-        <v>130</v>
-      </c>
-      <c r="K9" s="0" t="s">
-        <v>131</v>
-      </c>
-      <c r="M9" s="0" t="s">
-        <v>132</v>
-      </c>
-      <c r="R9" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="S9" s="0" t="s">
-        <v>134</v>
+      <c r="O9" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="T9" s="0" t="s">
+        <v>144</v>
       </c>
       <c r="U9" s="0" t="s">
-        <v>135</v>
-      </c>
-      <c r="X9" s="0" t="s">
-        <v>136</v>
+        <v>145</v>
+      </c>
+      <c r="W9" s="0" t="s">
+        <v>146</v>
       </c>
       <c r="Z9" s="0" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="AB9" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC9" s="0" t="s">
-        <v>138</v>
+        <v>148</v>
+      </c>
+      <c r="AD9" s="0" t="s">
+        <v>32</v>
       </c>
       <c r="AE9" s="0" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="AG9" s="0" t="s">
-        <v>140</v>
+        <v>150</v>
+      </c>
+      <c r="AI9" s="0" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1910,49 +2028,52 @@
         <v>9</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="C10" s="0" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>142</v>
-      </c>
-      <c r="M10" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="R10" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="S10" s="0" t="s">
-        <v>21</v>
+        <v>153</v>
+      </c>
+      <c r="L10" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="O10" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="T10" s="0" t="s">
+        <v>22</v>
       </c>
       <c r="U10" s="0" t="s">
-        <v>143</v>
-      </c>
-      <c r="X10" s="0" t="s">
-        <v>144</v>
+        <v>23</v>
+      </c>
+      <c r="W10" s="0" t="s">
+        <v>155</v>
       </c>
       <c r="Z10" s="0" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="AB10" s="0" t="s">
-        <v>146</v>
-      </c>
-      <c r="AC10" s="0" t="s">
-        <v>147</v>
+        <v>157</v>
+      </c>
+      <c r="AD10" s="0" t="s">
+        <v>158</v>
       </c>
       <c r="AE10" s="0" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="AG10" s="0" t="s">
-        <v>149</v>
+        <v>160</v>
+      </c>
+      <c r="AI10" s="0" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1960,46 +2081,49 @@
         <v>10</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C11" s="0" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="M11" s="0" t="s">
-        <v>152</v>
-      </c>
-      <c r="R11" s="0" t="s">
-        <v>153</v>
-      </c>
-      <c r="S11" s="0" t="s">
-        <v>154</v>
+        <v>163</v>
+      </c>
+      <c r="L11" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="O11" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="T11" s="0" t="s">
+        <v>166</v>
       </c>
       <c r="U11" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="X11" s="0" t="s">
-        <v>156</v>
+        <v>167</v>
+      </c>
+      <c r="W11" s="0" t="s">
+        <v>168</v>
       </c>
       <c r="Z11" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="AC11" s="0" t="s">
-        <v>158</v>
+        <v>169</v>
+      </c>
+      <c r="AB11" s="0" t="s">
+        <v>170</v>
       </c>
       <c r="AE11" s="0" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AG11" s="0" t="s">
-        <v>160</v>
+        <v>172</v>
+      </c>
+      <c r="AI11" s="0" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2013,40 +2137,43 @@
         <v>2</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>161</v>
-      </c>
-      <c r="M12" s="0" t="s">
-        <v>162</v>
-      </c>
-      <c r="R12" s="0" t="s">
-        <v>163</v>
-      </c>
-      <c r="S12" s="0" t="s">
-        <v>164</v>
+        <v>174</v>
+      </c>
+      <c r="L12" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="O12" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="T12" s="0" t="s">
+        <v>177</v>
       </c>
       <c r="U12" s="0" t="s">
-        <v>165</v>
-      </c>
-      <c r="X12" s="0" t="s">
-        <v>166</v>
+        <v>178</v>
+      </c>
+      <c r="W12" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="Z12" s="0" t="s">
-        <v>167</v>
-      </c>
-      <c r="AC12" s="0" t="s">
-        <v>168</v>
+        <v>180</v>
+      </c>
+      <c r="AB12" s="0" t="s">
+        <v>181</v>
       </c>
       <c r="AE12" s="0" t="s">
-        <v>33</v>
+        <v>182</v>
       </c>
       <c r="AG12" s="0" t="s">
-        <v>169</v>
+        <v>35</v>
+      </c>
+      <c r="AI12" s="0" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2054,40 +2181,43 @@
         <v>12</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C13" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="M13" s="0" t="s">
-        <v>171</v>
-      </c>
-      <c r="S13" s="0" t="s">
-        <v>172</v>
+        <v>185</v>
+      </c>
+      <c r="L13" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="O13" s="0" t="s">
+        <v>186</v>
       </c>
       <c r="U13" s="0" t="s">
-        <v>173</v>
-      </c>
-      <c r="X13" s="0" t="s">
-        <v>26</v>
+        <v>187</v>
+      </c>
+      <c r="W13" s="0" t="s">
+        <v>188</v>
       </c>
       <c r="Z13" s="0" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC13" s="0" t="s">
-        <v>175</v>
-      </c>
-      <c r="AG13" s="0" t="s">
-        <v>176</v>
+        <v>28</v>
+      </c>
+      <c r="AB13" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="AE13" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="AI13" s="0" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2095,34 +2225,37 @@
         <v>13</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C14" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>177</v>
-      </c>
-      <c r="M14" s="0" t="s">
-        <v>178</v>
-      </c>
-      <c r="U14" s="0" t="s">
-        <v>179</v>
-      </c>
-      <c r="X14" s="0" t="s">
-        <v>180</v>
+        <v>192</v>
+      </c>
+      <c r="L14" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="O14" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="W14" s="0" t="s">
+        <v>195</v>
       </c>
       <c r="Z14" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="AC14" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="AG14" s="0" t="s">
-        <v>182</v>
+        <v>196</v>
+      </c>
+      <c r="AB14" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="AE14" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI14" s="0" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2130,31 +2263,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C15" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>184</v>
-      </c>
-      <c r="M15" s="0" t="s">
-        <v>185</v>
-      </c>
-      <c r="U15" s="0" t="s">
-        <v>186</v>
-      </c>
-      <c r="Z15" s="0" t="s">
-        <v>187</v>
-      </c>
-      <c r="AC15" s="0" t="s">
-        <v>188</v>
-      </c>
-      <c r="AG15" s="0" t="s">
-        <v>189</v>
+        <v>200</v>
+      </c>
+      <c r="L15" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="O15" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="W15" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="AB15" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE15" s="0" t="s">
+        <v>204</v>
+      </c>
+      <c r="AI15" s="0" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2168,22 +2304,25 @@
         <v>3</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>190</v>
-      </c>
-      <c r="M16" s="0" t="s">
-        <v>191</v>
-      </c>
-      <c r="U16" s="0" t="s">
-        <v>192</v>
-      </c>
-      <c r="AC16" s="0" t="s">
-        <v>193</v>
-      </c>
-      <c r="AG16" s="0" t="s">
-        <v>194</v>
+        <v>206</v>
+      </c>
+      <c r="L16" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="O16" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="W16" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="AE16" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="AI16" s="0" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2191,25 +2330,28 @@
         <v>17</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C17" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>195</v>
-      </c>
-      <c r="U17" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC17" s="0" t="s">
-        <v>196</v>
-      </c>
-      <c r="AG17" s="0" t="s">
-        <v>197</v>
+        <v>212</v>
+      </c>
+      <c r="L17" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="W17" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE17" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="AI17" s="0" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2217,25 +2359,25 @@
         <v>18</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="C18" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>198</v>
-      </c>
-      <c r="U18" s="0" t="s">
-        <v>199</v>
-      </c>
-      <c r="AC18" s="0" t="s">
-        <v>200</v>
-      </c>
-      <c r="AG18" s="0" t="s">
-        <v>201</v>
+        <v>216</v>
+      </c>
+      <c r="W18" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="AE18" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="AI18" s="0" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2243,25 +2385,25 @@
         <v>19</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C19" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>202</v>
-      </c>
-      <c r="U19" s="0" t="s">
-        <v>203</v>
-      </c>
-      <c r="AC19" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="AG19" s="0" t="s">
-        <v>205</v>
+        <v>220</v>
+      </c>
+      <c r="W19" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="AE19" s="0" t="s">
+        <v>222</v>
+      </c>
+      <c r="AI19" s="0" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2269,25 +2411,25 @@
         <v>20</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C20" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>206</v>
-      </c>
-      <c r="U20" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="AC20" s="0" t="s">
-        <v>208</v>
-      </c>
-      <c r="AG20" s="0" t="s">
-        <v>209</v>
+        <v>224</v>
+      </c>
+      <c r="W20" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="AE20" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="AI20" s="0" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2295,25 +2437,25 @@
         <v>22</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="C21" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>210</v>
-      </c>
-      <c r="U21" s="0" t="s">
-        <v>211</v>
-      </c>
-      <c r="AC21" s="0" t="s">
-        <v>212</v>
-      </c>
-      <c r="AG21" s="0" t="s">
-        <v>213</v>
+        <v>228</v>
+      </c>
+      <c r="W21" s="0" t="s">
+        <v>229</v>
+      </c>
+      <c r="AE21" s="0" t="s">
+        <v>230</v>
+      </c>
+      <c r="AI21" s="0" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2321,19 +2463,19 @@
         <v>23</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="C22" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="U22" s="0" t="s">
-        <v>214</v>
-      </c>
-      <c r="AG22" s="0" t="s">
-        <v>215</v>
+        <v>31</v>
+      </c>
+      <c r="W22" s="0" t="s">
+        <v>232</v>
+      </c>
+      <c r="AI22" s="0" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2341,19 +2483,19 @@
         <v>24</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="C23" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="U23" s="0" t="s">
-        <v>216</v>
-      </c>
-      <c r="AG23" s="0" t="s">
-        <v>217</v>
+        <v>32</v>
+      </c>
+      <c r="W23" s="0" t="s">
+        <v>234</v>
+      </c>
+      <c r="AI23" s="0" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2361,19 +2503,19 @@
         <v>25</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="C24" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="U24" s="0" t="s">
-        <v>180</v>
-      </c>
-      <c r="AG24" s="0" t="s">
         <v>47</v>
+      </c>
+      <c r="W24" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI24" s="0" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2381,19 +2523,19 @@
         <v>26</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C25" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="U25" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG25" s="0" t="s">
-        <v>218</v>
+        <v>48</v>
+      </c>
+      <c r="W25" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="AI25" s="0" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2401,19 +2543,19 @@
         <v>27</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="C26" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="U26" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="AG26" s="0" t="s">
-        <v>220</v>
+        <v>35</v>
+      </c>
+      <c r="W26" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="AI26" s="0" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2427,10 +2569,10 @@
         <v>4</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="U27" s="0" t="s">
-        <v>221</v>
+        <v>36</v>
+      </c>
+      <c r="W27" s="0" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2438,16 +2580,16 @@
         <v>29</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C28" s="0" t="n">
         <v>4</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="U28" s="0" t="s">
-        <v>222</v>
+        <v>49</v>
+      </c>
+      <c r="W28" s="0" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2455,7 +2597,7 @@
         <v>30</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C29" s="0" t="n">
         <v>4</v>
@@ -2466,7 +2608,7 @@
         <v>31</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C30" s="0" t="n">
         <v>4</v>
@@ -2477,7 +2619,7 @@
         <v>32</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C31" s="0" t="n">
         <v>5</v>
@@ -2499,7 +2641,7 @@
         <v>34</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C33" s="0" t="n">
         <v>5</v>
@@ -2510,7 +2652,7 @@
         <v>35</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C34" s="0" t="n">
         <v>5</v>
@@ -2521,7 +2663,7 @@
         <v>36</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="C35" s="0" t="n">
         <v>5</v>
@@ -2532,7 +2674,7 @@
         <v>37</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="C36" s="0" t="n">
         <v>5</v>
@@ -2543,7 +2685,7 @@
         <v>38</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C37" s="0" t="n">
         <v>6</v>
@@ -2565,7 +2707,7 @@
         <v>41</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C39" s="0" t="n">
         <v>6</v>
@@ -2576,7 +2718,7 @@
         <v>42</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C40" s="0" t="n">
         <v>7</v>
@@ -2587,7 +2729,7 @@
         <v>43</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C41" s="0" t="n">
         <v>7</v>
@@ -2598,7 +2740,7 @@
         <v>44</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C42" s="0" t="n">
         <v>7</v>
@@ -2609,7 +2751,7 @@
         <v>45</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="C43" s="0" t="n">
         <v>7</v>
@@ -2620,7 +2762,7 @@
         <v>46</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C44" s="0" t="n">
         <v>7</v>
@@ -2631,7 +2773,7 @@
         <v>47</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="C45" s="0" t="n">
         <v>7</v>
@@ -2642,7 +2784,7 @@
         <v>48</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C46" s="0" t="n">
         <v>7</v>
@@ -2653,7 +2795,7 @@
         <v>49</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="C47" s="0" t="n">
         <v>7</v>
@@ -2664,7 +2806,7 @@
         <v>50</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="C48" s="0" t="n">
         <v>7</v>
@@ -2675,7 +2817,7 @@
         <v>51</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="C49" s="0" t="n">
         <v>7</v>
@@ -2686,7 +2828,7 @@
         <v>52</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="C50" s="0" t="n">
         <v>7</v>
@@ -2697,7 +2839,7 @@
         <v>53</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="C51" s="0" t="n">
         <v>7</v>
@@ -2708,7 +2850,7 @@
         <v>54</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="C52" s="0" t="n">
         <v>7</v>
@@ -2719,7 +2861,7 @@
         <v>55</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>8</v>
@@ -2730,7 +2872,7 @@
         <v>56</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>9</v>
@@ -2741,7 +2883,7 @@
         <v>57</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>9</v>
@@ -2752,7 +2894,7 @@
         <v>58</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C56" s="0" t="n">
         <v>9</v>
@@ -2763,7 +2905,7 @@
         <v>59</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C57" s="0" t="n">
         <v>10</v>
@@ -2774,7 +2916,7 @@
         <v>60</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C58" s="0" t="n">
         <v>10</v>
@@ -2785,7 +2927,7 @@
         <v>61</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C59" s="0" t="n">
         <v>10</v>
@@ -2796,7 +2938,7 @@
         <v>62</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C60" s="0" t="n">
         <v>10</v>
@@ -2807,7 +2949,7 @@
         <v>63</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="C61" s="0" t="n">
         <v>10</v>
@@ -2818,7 +2960,7 @@
         <v>64</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="C62" s="0" t="n">
         <v>10</v>
@@ -2829,7 +2971,7 @@
         <v>65</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C63" s="0" t="n">
         <v>10</v>
@@ -2840,7 +2982,7 @@
         <v>66</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="C64" s="0" t="n">
         <v>10</v>
@@ -2851,7 +2993,7 @@
         <v>67</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="C65" s="0" t="n">
         <v>10</v>
@@ -2862,7 +3004,7 @@
         <v>68</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C66" s="0" t="n">
         <v>11</v>
@@ -2873,7 +3015,7 @@
         <v>69</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C67" s="0" t="n">
         <v>11</v>
@@ -2884,7 +3026,7 @@
         <v>70</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C68" s="0" t="n">
         <v>11</v>
@@ -2895,7 +3037,7 @@
         <v>71</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C69" s="0" t="n">
         <v>11</v>
@@ -2906,7 +3048,7 @@
         <v>72</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="C70" s="0" t="n">
         <v>11</v>
@@ -2917,7 +3059,7 @@
         <v>73</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C71" s="0" t="n">
         <v>11</v>
@@ -2928,7 +3070,7 @@
         <v>74</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C72" s="0" t="n">
         <v>11</v>
@@ -2939,7 +3081,7 @@
         <v>75</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="C73" s="0" t="n">
         <v>11</v>
@@ -2950,7 +3092,7 @@
         <v>76</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="C74" s="0" t="n">
         <v>11</v>
@@ -2961,7 +3103,7 @@
         <v>77</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="C75" s="0" t="n">
         <v>11</v>
@@ -2972,7 +3114,7 @@
         <v>78</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C76" s="0" t="n">
         <v>12</v>
@@ -2983,7 +3125,7 @@
         <v>79</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C77" s="0" t="n">
         <v>13</v>
@@ -2994,7 +3136,7 @@
         <v>80</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C78" s="0" t="n">
         <v>13</v>
@@ -3005,7 +3147,7 @@
         <v>81</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C79" s="0" t="n">
         <v>13</v>
@@ -3016,7 +3158,7 @@
         <v>82</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="C80" s="0" t="n">
         <v>13</v>
@@ -3027,7 +3169,7 @@
         <v>83</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="C81" s="0" t="n">
         <v>13</v>
@@ -3038,7 +3180,7 @@
         <v>84</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="C82" s="0" t="n">
         <v>13</v>
@@ -3049,7 +3191,7 @@
         <v>85</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="C83" s="0" t="n">
         <v>13</v>
@@ -3060,7 +3202,7 @@
         <v>86</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="C84" s="0" t="n">
         <v>13</v>
@@ -3071,7 +3213,7 @@
         <v>87</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="C85" s="0" t="n">
         <v>13</v>
@@ -3082,7 +3224,7 @@
         <v>88</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="C86" s="0" t="n">
         <v>13</v>
@@ -3093,7 +3235,7 @@
         <v>89</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="C87" s="0" t="n">
         <v>13</v>
@@ -3104,7 +3246,7 @@
         <v>90</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="C88" s="0" t="n">
         <v>13</v>
@@ -3115,7 +3257,7 @@
         <v>91</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="C89" s="0" t="n">
         <v>13</v>
@@ -3126,7 +3268,7 @@
         <v>92</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C90" s="0" t="n">
         <v>13</v>
@@ -3137,7 +3279,7 @@
         <v>93</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="C91" s="0" t="n">
         <v>13</v>
@@ -3148,7 +3290,7 @@
         <v>94</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="C92" s="0" t="n">
         <v>13</v>
@@ -3159,7 +3301,7 @@
         <v>95</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="C93" s="0" t="n">
         <v>13</v>
@@ -3170,7 +3312,7 @@
         <v>96</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="C94" s="0" t="n">
         <v>13</v>
@@ -3181,7 +3323,7 @@
         <v>97</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="C95" s="0" t="n">
         <v>13</v>
@@ -3192,7 +3334,7 @@
         <v>98</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="C96" s="0" t="n">
         <v>13</v>
@@ -3203,7 +3345,7 @@
         <v>99</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="C97" s="0" t="n">
         <v>3</v>
@@ -3214,7 +3356,7 @@
         <v>100</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C98" s="0" t="n">
         <v>14</v>
@@ -3225,7 +3367,7 @@
         <v>101</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C99" s="0" t="n">
         <v>14</v>
@@ -3236,7 +3378,7 @@
         <v>102</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C100" s="0" t="n">
         <v>14</v>
@@ -3247,7 +3389,7 @@
         <v>103</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C101" s="0" t="n">
         <v>15</v>
@@ -3258,7 +3400,7 @@
         <v>104</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C102" s="0" t="n">
         <v>16</v>
@@ -3269,7 +3411,7 @@
         <v>105</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C103" s="0" t="n">
         <v>16</v>
@@ -3280,7 +3422,7 @@
         <v>106</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C104" s="0" t="n">
         <v>16</v>
@@ -3291,7 +3433,7 @@
         <v>107</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C105" s="0" t="n">
         <v>16</v>
@@ -3302,7 +3444,7 @@
         <v>108</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="C106" s="0" t="n">
         <v>16</v>
@@ -3313,7 +3455,7 @@
         <v>109</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="C107" s="0" t="n">
         <v>16</v>
@@ -3324,7 +3466,7 @@
         <v>110</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C108" s="0" t="n">
         <v>16</v>
@@ -3335,7 +3477,7 @@
         <v>111</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="C109" s="0" t="n">
         <v>16</v>
@@ -3346,7 +3488,7 @@
         <v>112</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="C110" s="0" t="n">
         <v>16</v>
@@ -3357,7 +3499,7 @@
         <v>113</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="C111" s="0" t="n">
         <v>16</v>
@@ -3368,7 +3510,7 @@
         <v>114</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="C112" s="0" t="n">
         <v>16</v>
@@ -3379,7 +3521,7 @@
         <v>115</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C113" s="0" t="n">
         <v>17</v>
@@ -3390,7 +3532,7 @@
         <v>116</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C114" s="0" t="n">
         <v>17</v>
@@ -3401,7 +3543,7 @@
         <v>117</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C115" s="0" t="n">
         <v>17</v>
@@ -3412,7 +3554,7 @@
         <v>118</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C116" s="0" t="n">
         <v>17</v>
@@ -3423,7 +3565,7 @@
         <v>119</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C117" s="0" t="n">
         <v>18</v>
@@ -3434,7 +3576,7 @@
         <v>120</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C118" s="0" t="n">
         <v>18</v>
@@ -3445,7 +3587,7 @@
         <v>121</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C119" s="0" t="n">
         <v>18</v>
@@ -3456,7 +3598,7 @@
         <v>122</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C120" s="0" t="n">
         <v>18</v>
@@ -3467,7 +3609,7 @@
         <v>123</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="C121" s="0" t="n">
         <v>18</v>
@@ -3478,7 +3620,7 @@
         <v>124</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C122" s="0" t="n">
         <v>18</v>
@@ -3489,7 +3631,7 @@
         <v>125</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="C123" s="0" t="n">
         <v>18</v>
@@ -3500,7 +3642,7 @@
         <v>126</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C124" s="0" t="n">
         <v>19</v>
@@ -3511,7 +3653,7 @@
         <v>127</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C125" s="0" t="n">
         <v>19</v>
@@ -3522,7 +3664,7 @@
         <v>128</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C126" s="0" t="n">
         <v>19</v>
@@ -3533,7 +3675,7 @@
         <v>129</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="C127" s="0" t="n">
         <v>19</v>
@@ -3544,7 +3686,7 @@
         <v>130</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="C128" s="0" t="n">
         <v>19</v>
@@ -3555,7 +3697,7 @@
         <v>131</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="C129" s="0" t="n">
         <v>19</v>
@@ -3566,7 +3708,7 @@
         <v>132</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="C130" s="0" t="n">
         <v>19</v>
@@ -3577,7 +3719,7 @@
         <v>133</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="C131" s="0" t="n">
         <v>19</v>
@@ -3588,7 +3730,7 @@
         <v>134</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="C132" s="0" t="n">
         <v>19</v>
@@ -3599,7 +3741,7 @@
         <v>135</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="C133" s="0" t="n">
         <v>19</v>
@@ -3610,7 +3752,7 @@
         <v>136</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C134" s="0" t="n">
         <v>19</v>
@@ -3621,7 +3763,7 @@
         <v>137</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="C135" s="0" t="n">
         <v>19</v>
@@ -3632,7 +3774,7 @@
         <v>138</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="C136" s="0" t="n">
         <v>19</v>
@@ -3643,7 +3785,7 @@
         <v>139</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="C137" s="0" t="n">
         <v>19</v>
@@ -3654,7 +3796,7 @@
         <v>140</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="C138" s="0" t="n">
         <v>19</v>
@@ -3665,7 +3807,7 @@
         <v>141</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="C139" s="0" t="n">
         <v>19</v>
@@ -3676,7 +3818,7 @@
         <v>142</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="C140" s="0" t="n">
         <v>19</v>
@@ -3687,7 +3829,7 @@
         <v>143</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C141" s="0" t="n">
         <v>20</v>
@@ -3698,7 +3840,7 @@
         <v>144</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C142" s="0" t="n">
         <v>25</v>
@@ -3709,7 +3851,7 @@
         <v>145</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C143" s="0" t="n">
         <v>20</v>
@@ -3720,7 +3862,7 @@
         <v>146</v>
       </c>
       <c r="B144" s="0" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C144" s="0" t="n">
         <v>20</v>
@@ -3731,7 +3873,7 @@
         <v>147</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C145" s="0" t="n">
         <v>20</v>
@@ -3742,7 +3884,7 @@
         <v>148</v>
       </c>
       <c r="B146" s="0" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C146" s="0" t="n">
         <v>21</v>
@@ -3753,7 +3895,7 @@
         <v>149</v>
       </c>
       <c r="B147" s="0" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C147" s="0" t="n">
         <v>21</v>
@@ -3764,7 +3906,7 @@
         <v>150</v>
       </c>
       <c r="B148" s="0" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C148" s="0" t="n">
         <v>21</v>
@@ -3775,7 +3917,7 @@
         <v>151</v>
       </c>
       <c r="B149" s="0" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C149" s="0" t="n">
         <v>21</v>
@@ -3786,7 +3928,7 @@
         <v>152</v>
       </c>
       <c r="B150" s="0" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="C150" s="0" t="n">
         <v>21</v>
@@ -3797,7 +3939,7 @@
         <v>153</v>
       </c>
       <c r="B151" s="0" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="C151" s="0" t="n">
         <v>21</v>
@@ -3808,7 +3950,7 @@
         <v>154</v>
       </c>
       <c r="B152" s="0" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="C152" s="0" t="n">
         <v>21</v>
@@ -3819,7 +3961,7 @@
         <v>155</v>
       </c>
       <c r="B153" s="0" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="C153" s="0" t="n">
         <v>21</v>
@@ -3830,7 +3972,7 @@
         <v>156</v>
       </c>
       <c r="B154" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C154" s="0" t="n">
         <v>21</v>
@@ -3841,7 +3983,7 @@
         <v>157</v>
       </c>
       <c r="B155" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C155" s="0" t="n">
         <v>22</v>
@@ -3852,7 +3994,7 @@
         <v>158</v>
       </c>
       <c r="B156" s="0" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C156" s="0" t="n">
         <v>23</v>
@@ -3863,7 +4005,7 @@
         <v>159</v>
       </c>
       <c r="B157" s="0" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C157" s="0" t="n">
         <v>23</v>
@@ -3874,7 +4016,7 @@
         <v>160</v>
       </c>
       <c r="B158" s="0" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="C158" s="0" t="n">
         <v>23</v>
@@ -3885,7 +4027,7 @@
         <v>161</v>
       </c>
       <c r="B159" s="0" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C159" s="0" t="n">
         <v>23</v>
@@ -3896,7 +4038,7 @@
         <v>162</v>
       </c>
       <c r="B160" s="0" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="C160" s="0" t="n">
         <v>23</v>
@@ -3907,7 +4049,7 @@
         <v>163</v>
       </c>
       <c r="B161" s="0" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="C161" s="0" t="n">
         <v>23</v>
@@ -3918,7 +4060,7 @@
         <v>164</v>
       </c>
       <c r="B162" s="0" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="C162" s="0" t="n">
         <v>23</v>
@@ -3929,7 +4071,7 @@
         <v>165</v>
       </c>
       <c r="B163" s="0" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="C163" s="0" t="n">
         <v>23</v>
@@ -3940,7 +4082,7 @@
         <v>166</v>
       </c>
       <c r="B164" s="0" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="C164" s="0" t="n">
         <v>23</v>
@@ -3951,7 +4093,7 @@
         <v>167</v>
       </c>
       <c r="B165" s="0" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="C165" s="0" t="n">
         <v>23</v>
@@ -3962,7 +4104,7 @@
         <v>168</v>
       </c>
       <c r="B166" s="0" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="C166" s="0" t="n">
         <v>23</v>
@@ -3973,7 +4115,7 @@
         <v>169</v>
       </c>
       <c r="B167" s="0" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="C167" s="0" t="n">
         <v>23</v>
@@ -3984,7 +4126,7 @@
         <v>170</v>
       </c>
       <c r="B168" s="0" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C168" s="0" t="n">
         <v>23</v>
@@ -3995,7 +4137,7 @@
         <v>171</v>
       </c>
       <c r="B169" s="0" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="C169" s="0" t="n">
         <v>23</v>
@@ -4006,7 +4148,7 @@
         <v>172</v>
       </c>
       <c r="B170" s="0" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="C170" s="0" t="n">
         <v>23</v>
@@ -4017,7 +4159,7 @@
         <v>173</v>
       </c>
       <c r="B171" s="0" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="C171" s="0" t="n">
         <v>23</v>
@@ -4028,7 +4170,7 @@
         <v>174</v>
       </c>
       <c r="B172" s="0" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="C172" s="0" t="n">
         <v>23</v>
@@ -4039,7 +4181,7 @@
         <v>175</v>
       </c>
       <c r="B173" s="0" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="C173" s="0" t="n">
         <v>23</v>
@@ -4050,7 +4192,7 @@
         <v>176</v>
       </c>
       <c r="B174" s="0" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="C174" s="0" t="n">
         <v>23</v>
@@ -4061,7 +4203,7 @@
         <v>177</v>
       </c>
       <c r="B175" s="0" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="C175" s="0" t="n">
         <v>23</v>
@@ -4072,7 +4214,7 @@
         <v>178</v>
       </c>
       <c r="B176" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C176" s="0" t="n">
         <v>23</v>
@@ -4083,7 +4225,7 @@
         <v>179</v>
       </c>
       <c r="B177" s="0" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="C177" s="0" t="n">
         <v>23</v>
@@ -4094,7 +4236,7 @@
         <v>180</v>
       </c>
       <c r="B178" s="0" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C178" s="0" t="n">
         <v>22</v>
@@ -4105,7 +4247,7 @@
         <v>181</v>
       </c>
       <c r="B179" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C179" s="0" t="n">
         <v>24</v>
@@ -4116,7 +4258,7 @@
         <v>182</v>
       </c>
       <c r="B180" s="0" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="C180" s="0" t="n">
         <v>19</v>
@@ -4127,7 +4269,7 @@
         <v>183</v>
       </c>
       <c r="B181" s="0" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="C181" s="0" t="n">
         <v>3</v>
@@ -4138,7 +4280,7 @@
         <v>184</v>
       </c>
       <c r="B182" s="0" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="C182" s="0" t="n">
         <v>23</v>
@@ -4149,7 +4291,7 @@
         <v>185</v>
       </c>
       <c r="B183" s="0" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="C183" s="0" t="n">
         <v>3</v>
@@ -4160,7 +4302,7 @@
         <v>186</v>
       </c>
       <c r="B184" s="0" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="C184" s="0" t="n">
         <v>3</v>
@@ -4171,7 +4313,7 @@
         <v>187</v>
       </c>
       <c r="B185" s="0" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C185" s="0" t="n">
         <v>26</v>
@@ -4182,7 +4324,7 @@
         <v>188</v>
       </c>
       <c r="B186" s="0" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C186" s="0" t="n">
         <v>26</v>
@@ -4193,7 +4335,7 @@
         <v>189</v>
       </c>
       <c r="B187" s="0" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C187" s="0" t="n">
         <v>26</v>
@@ -4204,7 +4346,7 @@
         <v>190</v>
       </c>
       <c r="B188" s="0" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C188" s="0" t="n">
         <v>26</v>
@@ -4215,7 +4357,7 @@
         <v>191</v>
       </c>
       <c r="B189" s="0" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="C189" s="0" t="n">
         <v>26</v>
@@ -4226,7 +4368,7 @@
         <v>192</v>
       </c>
       <c r="B190" s="0" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="C190" s="0" t="n">
         <v>26</v>
@@ -4237,7 +4379,7 @@
         <v>193</v>
       </c>
       <c r="B191" s="0" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="C191" s="0" t="n">
         <v>26</v>
@@ -4248,7 +4390,7 @@
         <v>194</v>
       </c>
       <c r="B192" s="0" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="C192" s="0" t="n">
         <v>26</v>
@@ -4259,7 +4401,7 @@
         <v>195</v>
       </c>
       <c r="B193" s="0" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="C193" s="0" t="n">
         <v>26</v>
@@ -4270,7 +4412,7 @@
         <v>196</v>
       </c>
       <c r="B194" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C194" s="0" t="n">
         <v>26</v>
@@ -4281,7 +4423,7 @@
         <v>197</v>
       </c>
       <c r="B195" s="0" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="C195" s="0" t="n">
         <v>26</v>
@@ -4292,7 +4434,7 @@
         <v>198</v>
       </c>
       <c r="B196" s="0" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="C196" s="0" t="n">
         <v>20</v>
@@ -4303,7 +4445,7 @@
         <v>199</v>
       </c>
       <c r="B197" s="0" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C197" s="0" t="n">
         <v>24</v>
@@ -4314,7 +4456,7 @@
         <v>200</v>
       </c>
       <c r="B198" s="0" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="C198" s="0" t="n">
         <v>13</v>
@@ -4325,7 +4467,7 @@
         <v>201</v>
       </c>
       <c r="B199" s="0" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="C199" s="0" t="n">
         <v>16</v>
@@ -4336,7 +4478,7 @@
         <v>202</v>
       </c>
       <c r="B200" s="0" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C200" s="0" t="n">
         <v>13</v>
@@ -4347,7 +4489,7 @@
         <v>203</v>
       </c>
       <c r="B201" s="0" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="C201" s="0" t="n">
         <v>13</v>
@@ -4358,7 +4500,7 @@
         <v>204</v>
       </c>
       <c r="B202" s="0" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="C202" s="0" t="n">
         <v>13</v>
@@ -4369,16 +4511,225 @@
         <v>205</v>
       </c>
       <c r="B203" s="0" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="C203" s="0" t="n">
         <v>13</v>
       </c>
     </row>
+    <row r="204" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="0" t="n">
+        <v>251</v>
+      </c>
+      <c r="B204" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="C204" s="0" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="0" t="n">
+        <v>239</v>
+      </c>
+      <c r="B205" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C205" s="0" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="0" t="n">
+        <v>240</v>
+      </c>
+      <c r="B206" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="C206" s="0" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="0" t="n">
+        <v>241</v>
+      </c>
+      <c r="B207" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="C207" s="0" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="0" t="n">
+        <v>242</v>
+      </c>
+      <c r="B208" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="C208" s="0" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="0" t="n">
+        <v>243</v>
+      </c>
+      <c r="B209" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="C209" s="0" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="0" t="n">
+        <v>244</v>
+      </c>
+      <c r="B210" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C210" s="0" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="0" t="n">
+        <v>245</v>
+      </c>
+      <c r="B211" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="C211" s="0" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="0" t="n">
+        <v>246</v>
+      </c>
+      <c r="B212" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="C212" s="0" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="0" t="n">
+        <v>247</v>
+      </c>
+      <c r="B213" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="C213" s="0" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="0" t="n">
+        <v>248</v>
+      </c>
+      <c r="B214" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="C214" s="0" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="0" t="n">
+        <v>249</v>
+      </c>
+      <c r="B215" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="C215" s="0" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="0" t="n">
+        <v>251</v>
+      </c>
+      <c r="B216" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="C216" s="0" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="0" t="n">
+        <v>252</v>
+      </c>
+      <c r="B217" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="C217" s="0" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="0" t="n">
+        <v>253</v>
+      </c>
+      <c r="B218" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="C218" s="0" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="0" t="n">
+        <v>254</v>
+      </c>
+      <c r="B219" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="C219" s="0" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="0" t="n">
+        <v>255</v>
+      </c>
+      <c r="B220" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="C220" s="0" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="0" t="n">
+        <v>256</v>
+      </c>
+      <c r="B221" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="C221" s="0" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="0" t="n">
+        <v>257</v>
+      </c>
+      <c r="B222" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C222" s="0" t="n">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AG203"/>
+  <autoFilter ref="A1:AI203"/>
   <mergeCells count="1">
-    <mergeCell ref="G2:AG2"/>
+    <mergeCell ref="G2:AI2"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -4397,119 +4748,158 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32.11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>239</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>244</v>
+        <v>263</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Página &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/static/modelos/descricao_lote_imp.xlsx
+++ b/static/modelos/descricao_lote_imp.xlsx
@@ -815,7 +815,7 @@
     <t xml:space="preserve">Operador</t>
   </si>
   <si>
-    <t xml:space="preserve">Presidente</t>
+    <t xml:space="preserve">Presidente/CEO</t>
   </si>
   <si>
     <t xml:space="preserve">Profissional de Nível Superior Junior</t>
@@ -980,7 +980,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66796875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.33"/>
@@ -1059,7 +1059,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66796875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.89"/>
   </cols>
@@ -1086,7 +1086,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66796875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="13.33"/>
   </cols>
@@ -1113,7 +1113,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66796875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28.33"/>
@@ -1366,7 +1366,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AI222"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66796875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46.1"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="0" width="28.33"/>
@@ -4748,7 +4748,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66796875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32.11"/>
   </cols>
@@ -4880,7 +4880,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
